--- a/Practicos/Rodriguez Theo/Notas y devoluciones.xlsx
+++ b/Practicos/Rodriguez Theo/Notas y devoluciones.xlsx
@@ -18,7 +18,53 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="4">
+  <si>
+    <t>Nota: 9</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+        <sz val="12.0"/>
+      </rPr>
+      <t xml:space="preserve">
+🎉¡Felicitaciones por la entrega del Desafío 01! 🎉
+Primeramente, quería felicitarte por el trabajo que realizaste. El resultado renderizado es el solicitado.
+Destaco la correcta estructura del documento HTML, el manejo de listas desordenadas y ordenadas es correcto.
+Respetaste el orden de aplicación de uso de etiquetas de encabezado (h1, h2, etc..) y el manejo de etiquetas para textos es correcto. 
+Buenísimo que hayas diferenciado cuando usar etiquetas &lt;strong&gt; y &lt;b&gt; 
+Observaciones a tu trabajo son:
+•        Recorda cambiar el lenguaje a español &lt;html lang="es"&gt; porque esto le dice a los motores de búsqueda en que idioma esta tu sitio web.
+•        Recaudo con el uso de la etiqueta &lt;strong&gt;, recorda que le dice a los motores de búsqueda que esa info es importante y que la tome en cuenta cuando imprime los resultados de búsqueda, por lo cual es recomendable utilizarla con recaudo. Por ejemplo en la parte del significado del término MERN que la primer letra del item va en negrita podes utilizar en lugar de &lt;strong&gt; la etiqueta &lt;b&gt; que pone en negrita la letra pero con un fin mas que todo de estética visual para el usuario:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color rgb="FF0000FF"/>
+        <sz val="12.0"/>
+      </rPr>
+      <t xml:space="preserve">        &lt;ul&gt;
+             &lt;li&gt;&lt;b&gt;M&lt;/b&gt;ongoDB….&lt;/li&gt;
+              ….. 
+              ….
+             &lt;li&gt;&lt;b&gt;N&lt;/bode.js….&lt;/li&gt;  
+       &lt;/ul&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+        <sz val="12.0"/>
+      </rPr>
+      <t xml:space="preserve">
+Muy buen trabajo ¡
+Tu nota en el Desafío 01 es: 9
+</t>
+    </r>
+  </si>
   <si>
     <t>Nota:</t>
   </si>
@@ -30,7 +76,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="3">
+  <fonts count="5">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -39,10 +85,21 @@
     </font>
     <font>
       <b/>
+      <sz val="14.0"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font/>
+    <font>
+      <sz val="12.0"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <color theme="1"/>
+      <name val="Arial"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -140,15 +197,17 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
     <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="3" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="4" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="top"/>
+    <xf borderId="4" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="5" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="6" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
@@ -157,6 +216,10 @@
     <xf borderId="9" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="10" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="11" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -378,7 +441,8 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="6" width="12.63"/>
+    <col customWidth="1" min="1" max="5" width="12.63"/>
+    <col customWidth="1" min="6" max="6" width="20.75"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1"/>
@@ -406,19 +470,19 @@
       <c r="A4" s="7"/>
       <c r="F4" s="8"/>
     </row>
-    <row r="5" ht="15.75" customHeight="1">
+    <row r="5" ht="104.25" customHeight="1">
       <c r="A5" s="7"/>
       <c r="F5" s="8"/>
     </row>
-    <row r="6" ht="15.75" customHeight="1">
+    <row r="6" ht="104.25" customHeight="1">
       <c r="A6" s="7"/>
       <c r="F6" s="8"/>
     </row>
-    <row r="7" ht="15.75" customHeight="1">
+    <row r="7" ht="190.5" customHeight="1">
       <c r="A7" s="7"/>
       <c r="F7" s="8"/>
     </row>
-    <row r="8" ht="15.75" customHeight="1">
+    <row r="8" ht="190.5" customHeight="1">
       <c r="A8" s="9"/>
       <c r="B8" s="10"/>
       <c r="C8" s="10"/>
@@ -1439,8 +1503,8 @@
   <sheetData>
     <row r="1" ht="15.75" customHeight="1"/>
     <row r="2" ht="15.75" customHeight="1">
-      <c r="A2" s="1" t="s">
-        <v>0</v>
+      <c r="A2" s="12" t="s">
+        <v>2</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -1449,8 +1513,8 @@
       <c r="F2" s="3"/>
     </row>
     <row r="3" ht="15.75" customHeight="1">
-      <c r="A3" s="4" t="s">
-        <v>1</v>
+      <c r="A3" s="13" t="s">
+        <v>3</v>
       </c>
       <c r="B3" s="5"/>
       <c r="C3" s="5"/>
@@ -2496,8 +2560,8 @@
   <sheetData>
     <row r="1" ht="15.75" customHeight="1"/>
     <row r="2" ht="15.75" customHeight="1">
-      <c r="A2" s="1" t="s">
-        <v>0</v>
+      <c r="A2" s="12" t="s">
+        <v>2</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -2506,8 +2570,8 @@
       <c r="F2" s="3"/>
     </row>
     <row r="3" ht="15.75" customHeight="1">
-      <c r="A3" s="4" t="s">
-        <v>1</v>
+      <c r="A3" s="13" t="s">
+        <v>3</v>
       </c>
       <c r="B3" s="5"/>
       <c r="C3" s="5"/>
